--- a/artfynd/A 37137-2023 artfynd.xlsx
+++ b/artfynd/A 37137-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37137-2023 artfynd.xlsx
+++ b/artfynd/A 37137-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2248,6 +2248,118 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125253748</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91579</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>760</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Blausjaurliden, Blausjaurliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>673309</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7239188</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Malå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Landström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Landström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37137-2023 artfynd.xlsx
+++ b/artfynd/A 37137-2023 artfynd.xlsx
@@ -2253,7 +2253,7 @@
         <v>125253748</v>
       </c>
       <c r="B16" t="n">
-        <v>91579</v>
+        <v>91737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2023 artfynd.xlsx
+++ b/artfynd/A 37137-2023 artfynd.xlsx
@@ -2253,12 +2253,7 @@
         <v>125253748</v>
       </c>
       <c r="B16" t="n">
-        <v>91737</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2023 artfynd.xlsx
+++ b/artfynd/A 37137-2023 artfynd.xlsx
@@ -2253,7 +2253,7 @@
         <v>125253748</v>
       </c>
       <c r="B16" t="n">
-        <v>91791</v>
+        <v>91798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37137-2023 artfynd.xlsx
+++ b/artfynd/A 37137-2023 artfynd.xlsx
@@ -2253,7 +2253,7 @@
         <v>125253748</v>
       </c>
       <c r="B16" t="n">
-        <v>91798</v>
+        <v>91802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
